--- a/premise/data/additional_inventories/lci-rhenium.xlsx
+++ b/premise/data/additional_inventories/lci-rhenium.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hahnme_a\PycharmProjects\premise\premise\data\additional_inventories\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32707A0A-D73A-4F1D-87A5-C0E2265D6EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9815414-EF3E-4D7D-A019-AB4EFF086BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-60" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="rhenium" sheetId="1" r:id="rId1"/>
@@ -476,7 +476,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="174" formatCode="0.0000000"/>
+    <numFmt numFmtId="164" formatCode="0.0000000"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -565,10 +565,10 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -986,8 +986,8 @@
         <v>82</v>
       </c>
       <c r="B12" s="14">
-        <f>H12*0.07/0.9509/$H$11</f>
-        <v>7.5784534816423303E-5</v>
+        <f>H12*0.07/95.09/$H$11</f>
+        <v>7.5784534816423306E-7</v>
       </c>
       <c r="C12" t="s">
         <v>6</v>
@@ -1011,8 +1011,8 @@
         <v>70</v>
       </c>
       <c r="B13" s="14">
-        <f t="shared" ref="B13:B76" si="0">H13*0.07/0.9509/$H$11</f>
-        <v>2.0468967736776197E-2</v>
+        <f t="shared" ref="B13:B76" si="0">H13*0.07/95.09/$H$11</f>
+        <v>2.0468967736776193E-4</v>
       </c>
       <c r="C13" t="s">
         <v>7</v>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="B14" s="14">
         <f t="shared" si="0"/>
-        <v>7574.2638534545513</v>
+        <v>75.742638534545506</v>
       </c>
       <c r="C14" t="s">
         <v>7</v>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B15" s="14">
         <f t="shared" si="0"/>
-        <v>1.5753017169421294E-2</v>
+        <v>1.5753017169421296E-4</v>
       </c>
       <c r="C15" t="s">
         <v>7</v>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="B16" s="14">
         <f t="shared" si="0"/>
-        <v>5825.4473288128647</v>
+        <v>58.254473288128636</v>
       </c>
       <c r="C16" t="s">
         <v>7</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B17" s="14">
         <f t="shared" si="0"/>
-        <v>2037.8050345122117</v>
+        <v>20.378050345122116</v>
       </c>
       <c r="C17" t="s">
         <v>7</v>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B18" s="14">
         <f t="shared" si="0"/>
-        <v>0.68249897759501399</v>
+        <v>6.8249897759501393E-3</v>
       </c>
       <c r="C18" t="s">
         <v>59</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B19" s="14">
         <f t="shared" si="0"/>
-        <v>7.0035766196542087E-2</v>
+        <v>7.0035766196542082E-4</v>
       </c>
       <c r="C19" t="s">
         <v>7</v>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B20" s="14">
         <f t="shared" si="0"/>
-        <v>3.4799847019721657E-2</v>
+        <v>3.4799847019721653E-4</v>
       </c>
       <c r="C20" t="s">
         <v>7</v>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="B21" s="14">
         <f t="shared" si="0"/>
-        <v>495.28408151531085</v>
+        <v>4.9528408151531078</v>
       </c>
       <c r="C21" t="s">
         <v>17</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="B22" s="14">
         <f t="shared" si="0"/>
-        <v>3.4100737587298736E-2</v>
+        <v>3.4100737587298735E-4</v>
       </c>
       <c r="C22" t="s">
         <v>7</v>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B23" s="14">
         <f t="shared" si="0"/>
-        <v>116937.41886882656</v>
+        <v>1169.3741886882656</v>
       </c>
       <c r="C23" t="s">
         <v>15</v>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B24" s="14">
         <f t="shared" si="0"/>
-        <v>65481.178427797509</v>
+        <v>654.81178427797499</v>
       </c>
       <c r="C24" t="s">
         <v>15</v>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B25" s="14">
         <f t="shared" si="0"/>
-        <v>0.28782774458452803</v>
+        <v>2.8782774458452807E-3</v>
       </c>
       <c r="C25" t="s">
         <v>7</v>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B26" s="14">
         <f t="shared" si="0"/>
-        <v>9829.4208874972064</v>
+        <v>98.294208874972043</v>
       </c>
       <c r="C26" t="s">
         <v>7</v>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B27" s="14">
         <f t="shared" si="0"/>
-        <v>8.5113951634554127E-5</v>
+        <v>8.5113951634554124E-7</v>
       </c>
       <c r="C27" t="s">
         <v>6</v>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="B28" s="14">
         <f t="shared" si="0"/>
-        <v>3.7132682421164448E-5</v>
+        <v>3.7132682421164447E-7</v>
       </c>
       <c r="C28" t="s">
         <v>6</v>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="B29" s="14">
         <f t="shared" si="0"/>
-        <v>-15490200.547525952</v>
+        <v>-154902.00547525947</v>
       </c>
       <c r="C29" t="s">
         <v>7</v>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B30" s="14">
         <f t="shared" si="0"/>
-        <v>3.3367754549774132E-4</v>
+        <v>3.336775454977413E-6</v>
       </c>
       <c r="C30" t="s">
         <v>7</v>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="B31" s="14">
         <f t="shared" si="0"/>
-        <v>265.59037721154476</v>
+        <v>2.6559037721154475</v>
       </c>
       <c r="C31" t="s">
         <v>7</v>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B32" s="14">
         <f t="shared" si="0"/>
-        <v>6525.2900515601223</v>
+        <v>65.252900515601212</v>
       </c>
       <c r="C32" t="s">
         <v>7</v>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B33" s="14">
         <f t="shared" si="0"/>
-        <v>-8773923.1011663582</v>
+        <v>-87739.231011663564</v>
       </c>
       <c r="C33" t="s">
         <v>7</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B34" s="14">
         <f t="shared" si="0"/>
-        <v>5.087165083642041E-2</v>
+        <v>5.0871650836420402E-4</v>
       </c>
       <c r="C34" t="s">
         <v>7</v>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="B35" s="14">
         <f t="shared" si="0"/>
-        <v>0.13847202668331651</v>
+        <v>1.384720266833165E-3</v>
       </c>
       <c r="C35" t="s">
         <v>7</v>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="B36" s="14">
         <f t="shared" si="0"/>
-        <v>8.2384918467582344E-4</v>
+        <v>8.2384918467582337E-6</v>
       </c>
       <c r="C36" t="s">
         <v>7</v>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="B37" s="14">
         <f t="shared" si="0"/>
-        <v>6.1788688850686812E-3</v>
+        <v>6.1788688850686804E-5</v>
       </c>
       <c r="C37" t="s">
         <v>7</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="B38" s="14">
         <f t="shared" si="0"/>
-        <v>4.7299826178038608E-3</v>
+        <v>4.7299826178038596E-5</v>
       </c>
       <c r="C38" t="s">
         <v>7</v>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="B39" s="14">
         <f t="shared" si="0"/>
-        <v>1.7081458599852634E-6</v>
+        <v>1.7081458599852633E-8</v>
       </c>
       <c r="C39" t="s">
         <v>7</v>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B40" s="14">
         <f t="shared" si="0"/>
-        <v>1.0716106310190961E-2</v>
+        <v>1.071610631019096E-4</v>
       </c>
       <c r="C40" t="s">
         <v>7</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="B41" s="14">
         <f t="shared" si="0"/>
-        <v>16.702790328954471</v>
+        <v>0.16702790328954467</v>
       </c>
       <c r="C41" t="s">
         <v>7</v>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="B42" s="14">
         <f t="shared" si="0"/>
-        <v>4.1192459233791091E-2</v>
+        <v>4.1192459233791091E-4</v>
       </c>
       <c r="C42" t="s">
         <v>7</v>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B43" s="14">
         <f t="shared" si="0"/>
-        <v>4.531170515717034E-4</v>
+        <v>4.5311705157170327E-6</v>
       </c>
       <c r="C43" t="s">
         <v>7</v>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B44" s="14">
         <f t="shared" si="0"/>
-        <v>5.0617956870078963E-4</v>
+        <v>5.0617956870078966E-6</v>
       </c>
       <c r="C44" t="s">
         <v>7</v>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="B45" s="14">
         <f t="shared" si="0"/>
-        <v>1099.6407248190355</v>
+        <v>10.996407248190355</v>
       </c>
       <c r="C45" t="s">
         <v>7</v>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="B46" s="14">
         <f t="shared" si="0"/>
-        <v>5111.7512057556696</v>
+        <v>51.117512057556688</v>
       </c>
       <c r="C46" t="s">
         <v>7</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="B47" s="14">
         <f t="shared" si="0"/>
-        <v>895.48824421285246</v>
+        <v>8.9548824421285236</v>
       </c>
       <c r="C47" t="s">
         <v>7</v>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B48" s="14">
         <f t="shared" si="0"/>
-        <v>0.41192459233791096</v>
+        <v>4.119245923379109E-3</v>
       </c>
       <c r="C48" t="s">
         <v>7</v>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="B49" s="14">
         <f t="shared" si="0"/>
-        <v>8.7628933939213585E-4</v>
+        <v>8.7628933939213572E-6</v>
       </c>
       <c r="C49" t="s">
         <v>7</v>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="B50" s="14">
         <f t="shared" si="0"/>
-        <v>8.2384918467582544E-2</v>
+        <v>8.2384918467582528E-4</v>
       </c>
       <c r="C50" t="s">
         <v>7</v>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="B51" s="14">
         <f t="shared" si="0"/>
-        <v>1.2520686994734256E-3</v>
+        <v>1.2520686994734255E-5</v>
       </c>
       <c r="C51" t="s">
         <v>7</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="B52" s="14">
         <f t="shared" si="0"/>
-        <v>16.702592448795588</v>
+        <v>0.16702592448795586</v>
       </c>
       <c r="C52" t="s">
         <v>7</v>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="B53" s="14">
         <f t="shared" si="0"/>
-        <v>48295.519981975332</v>
+        <v>482.95519981975332</v>
       </c>
       <c r="C53" t="s">
         <v>7</v>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="B54" s="14">
         <f t="shared" si="0"/>
-        <v>0.20596229616895548</v>
+        <v>2.0596229616895545E-3</v>
       </c>
       <c r="C54" t="s">
         <v>7</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="B55" s="14">
         <f t="shared" si="0"/>
-        <v>1.2689913781148619E-2</v>
+        <v>1.2689913781148616E-4</v>
       </c>
       <c r="C55" t="s">
         <v>7</v>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="B56" s="14">
         <f t="shared" si="0"/>
-        <v>5.185220216209793E-11</v>
+        <v>5.1852202162097937E-13</v>
       </c>
       <c r="C56" t="s">
         <v>7</v>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="B57" s="14">
         <f t="shared" si="0"/>
-        <v>5.4752727557276648</v>
+        <v>5.4752727557276636E-2</v>
       </c>
       <c r="C57" t="s">
         <v>7</v>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="B58" s="14">
         <f t="shared" si="0"/>
-        <v>8.2832456489420867</v>
+        <v>8.2832456489420864E-2</v>
       </c>
       <c r="C58" t="s">
         <v>7</v>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="B59" s="14">
         <f t="shared" si="0"/>
-        <v>6.5342033229306526</v>
+        <v>6.5342033229306526E-2</v>
       </c>
       <c r="C59" t="s">
         <v>7</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="B60" s="14">
         <f t="shared" si="0"/>
-        <v>3.9132836272101557</v>
+        <v>3.9132836272101547E-2</v>
       </c>
       <c r="C60" t="s">
         <v>7</v>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="B61" s="14">
         <f t="shared" si="0"/>
-        <v>17071478.326140258</v>
+        <v>170714.7832614026</v>
       </c>
       <c r="C61" t="s">
         <v>7</v>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="B62" s="14">
         <f t="shared" si="0"/>
-        <v>0.45839417672663574</v>
+        <v>4.5839417672663575E-3</v>
       </c>
       <c r="C62" t="s">
         <v>7</v>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="B63" s="14">
         <f t="shared" si="0"/>
-        <v>0.46585707077751004</v>
+        <v>4.6585707077750997E-3</v>
       </c>
       <c r="C63" t="s">
         <v>7</v>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B64" s="14">
         <f t="shared" si="0"/>
-        <v>5.7669442927307732E-2</v>
+        <v>5.7669442927307725E-4</v>
       </c>
       <c r="C64" t="s">
         <v>7</v>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="B65" s="14">
         <f t="shared" si="0"/>
-        <v>4.4853146619492036E-3</v>
+        <v>4.4853146619492032E-5</v>
       </c>
       <c r="C65" t="s">
         <v>7</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="B66" s="14">
         <f t="shared" si="0"/>
-        <v>3.9132836272101557</v>
+        <v>3.9132836272101547E-2</v>
       </c>
       <c r="C66" t="s">
         <v>7</v>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="B67" s="14">
         <f t="shared" si="0"/>
-        <v>3.9530762529621233E-2</v>
+        <v>3.9530762529621228E-4</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>7</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="B68" s="14">
         <f t="shared" si="0"/>
-        <v>2.0596229616895545E-4</v>
+        <v>2.0596229616895542E-6</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>7</v>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="B69" s="14">
         <f t="shared" si="0"/>
-        <v>6.0337712837649404E-5</v>
+        <v>6.0337712837649413E-7</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>7</v>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B70" s="14">
         <f t="shared" si="0"/>
-        <v>749.9250423387158</v>
+        <v>7.4992504233871573</v>
       </c>
       <c r="C70" s="8" t="s">
         <v>7</v>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="B71" s="14">
         <f t="shared" si="0"/>
-        <v>1.3125615109276808E-9</v>
+        <v>1.3125615109276806E-11</v>
       </c>
       <c r="C71" s="8" t="s">
         <v>7</v>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="B72" s="14">
         <f t="shared" si="0"/>
-        <v>0.3295396738703294</v>
+        <v>3.2953967387032938E-3</v>
       </c>
       <c r="C72" s="8" t="s">
         <v>7</v>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="B73" s="14">
         <f t="shared" si="0"/>
-        <v>3.898878105001051E-2</v>
+        <v>3.8988781050010508E-4</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>7</v>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="B74" s="14">
         <f t="shared" si="0"/>
-        <v>4.9121293348748452E-3</v>
+        <v>4.9121293348748456E-5</v>
       </c>
       <c r="C74" s="8" t="s">
         <v>7</v>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B75" s="14">
         <f t="shared" si="0"/>
-        <v>36.454786583202235</v>
+        <v>0.36454786583202231</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>7</v>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="B76" s="14">
         <f t="shared" si="0"/>
-        <v>471.34912940012015</v>
+        <v>4.7134912940012015</v>
       </c>
       <c r="C76" s="8" t="s">
         <v>64</v>
@@ -2484,8 +2484,8 @@
         <v>133</v>
       </c>
       <c r="B77" s="14">
-        <f t="shared" ref="B77:B94" si="1">H77*0.07/0.9509/$H$11</f>
-        <v>202.47964625339696</v>
+        <f t="shared" ref="B77:B94" si="1">H77*0.07/95.09/$H$11</f>
+        <v>2.0247964625339696</v>
       </c>
       <c r="C77" s="8" t="s">
         <v>7</v>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="B78" s="14">
         <f t="shared" si="1"/>
-        <v>2094.6018474484154</v>
+        <v>20.946018474484152</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>7</v>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="B79" s="14">
         <f t="shared" si="1"/>
-        <v>1822.1644296773231</v>
+        <v>18.221644296773231</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>7</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="B80" s="14">
         <f t="shared" si="1"/>
-        <v>134.92190840101117</v>
+        <v>1.3492190840101115</v>
       </c>
       <c r="C80" s="8" t="s">
         <v>7</v>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="B81" s="14">
         <f t="shared" si="1"/>
-        <v>2.0596229616895545E-4</v>
+        <v>2.0596229616895542E-6</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>7</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="B82" s="14">
         <f t="shared" si="1"/>
-        <v>16.318832691468291</v>
+        <v>0.16318832691468291</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>7</v>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="B83" s="14">
         <f t="shared" si="1"/>
-        <v>3777.8017777033665</v>
+        <v>37.778017777033668</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>7</v>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="B84" s="14">
         <f t="shared" si="1"/>
-        <v>11.623023858342311</v>
+        <v>0.11623023858342309</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>7</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B85" s="14">
         <f t="shared" si="1"/>
-        <v>6.5339871511881444</v>
+        <v>6.5339871511881448E-2</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>7</v>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="B86" s="14">
         <f t="shared" si="1"/>
-        <v>15.671044273724918</v>
+        <v>0.15671044273724918</v>
       </c>
       <c r="C86" s="8" t="s">
         <v>65</v>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="B87" s="14">
         <f t="shared" si="1"/>
-        <v>15.671044273724918</v>
+        <v>0.15671044273724918</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>65</v>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="B88" s="14">
         <f t="shared" si="1"/>
-        <v>801.80347589054361</v>
+        <v>8.0180347589054364</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>22</v>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="B89" s="14">
         <f t="shared" si="1"/>
-        <v>5.0682215607290811E-2</v>
+        <v>5.0682215607290805E-4</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>22</v>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="B90" s="14">
         <f t="shared" si="1"/>
-        <v>801.79453197014232</v>
+        <v>8.0179453197014237</v>
       </c>
       <c r="C90" t="s">
         <v>22</v>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="B91" s="14">
         <f t="shared" si="1"/>
-        <v>8899.8549622233986</v>
+        <v>88.998549622233966</v>
       </c>
       <c r="C91" t="s">
         <v>22</v>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="B92" s="14">
         <f t="shared" si="1"/>
-        <v>8.9820480457371191E-2</v>
+        <v>8.9820480457371179E-4</v>
       </c>
       <c r="C92" t="s">
         <v>22</v>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="B93" s="14">
         <f t="shared" si="1"/>
-        <v>0.78265672544203291</v>
+        <v>7.8265672544203281E-3</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>7</v>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="B94" s="14">
         <f t="shared" si="1"/>
-        <v>0.12159602569199424</v>
+        <v>1.2159602569199422E-3</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>7</v>
@@ -4899,8 +4899,8 @@
         <v>82</v>
       </c>
       <c r="B201" s="14">
-        <f t="shared" ref="B201:B222" si="4">H201*0.09/0.8121/$H$224</f>
-        <v>1.0151685725046852E-4</v>
+        <f>H201*0.09/81.21/$H$224</f>
+        <v>1.0151685725046853E-6</v>
       </c>
       <c r="C201" t="s">
         <v>6</v>
@@ -4923,8 +4923,8 @@
         <v>70</v>
       </c>
       <c r="B202" s="14">
-        <f t="shared" si="4"/>
-        <v>2.741912028400325E-2</v>
+        <f t="shared" ref="B202:B223" si="4">H202*0.09/81.21/$H$224</f>
+        <v>2.7419120284003249E-4</v>
       </c>
       <c r="C202" t="s">
         <v>7</v>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="B203" s="14">
         <f t="shared" si="4"/>
-        <v>7093.2341500717639</v>
+        <v>70.932341500717641</v>
       </c>
       <c r="C203" t="s">
         <v>7</v>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="B204" s="14">
         <f t="shared" si="4"/>
-        <v>1.4752567578147181E-2</v>
+        <v>1.4752567578147185E-4</v>
       </c>
       <c r="C204" t="s">
         <v>7</v>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="B205" s="14">
         <f t="shared" si="4"/>
-        <v>5455.4822398130927</v>
+        <v>54.554822398130938</v>
       </c>
       <c r="C205" t="s">
         <v>7</v>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="B206" s="14">
         <f t="shared" si="4"/>
-        <v>2729.7332271548257</v>
+        <v>27.297332271548264</v>
       </c>
       <c r="C206" t="s">
         <v>7</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="B207" s="14">
         <f t="shared" si="4"/>
-        <v>0.91423865634244217</v>
+        <v>9.1423865634244223E-3</v>
       </c>
       <c r="C207" t="s">
         <v>59</v>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="B208" s="14">
         <f t="shared" si="4"/>
-        <v>6.5587903738681619E-2</v>
+        <v>6.5587903738681624E-4</v>
       </c>
       <c r="C208" t="s">
         <v>7</v>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="B209" s="14">
         <f t="shared" si="4"/>
-        <v>3.2589762922634297E-2</v>
+        <v>3.2589762922634292E-4</v>
       </c>
       <c r="C209" t="s">
         <v>7</v>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="B210" s="14">
         <f t="shared" si="4"/>
-        <v>463.82936070929202</v>
+        <v>4.6382936070929208</v>
       </c>
       <c r="C210" t="s">
         <v>17</v>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="B211" s="14">
         <f t="shared" si="4"/>
-        <v>4.567950068138836E-2</v>
+        <v>4.5679500681388362E-4</v>
       </c>
       <c r="C211" t="s">
         <v>7</v>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="B212" s="14">
         <f t="shared" si="4"/>
-        <v>156643.03128997152</v>
+        <v>1566.4303128997158</v>
       </c>
       <c r="C212" t="s">
         <v>15</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="B213" s="14">
         <f t="shared" si="4"/>
-        <v>61322.570747143101</v>
+        <v>613.22570747143106</v>
       </c>
       <c r="C213" t="s">
         <v>15</v>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="B214" s="14">
         <f t="shared" si="4"/>
-        <v>0.26954825270497235</v>
+        <v>2.6954825270497237E-3</v>
       </c>
       <c r="C214" t="s">
         <v>7</v>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="B215" s="14">
         <f t="shared" si="4"/>
-        <v>9205.1696724063804</v>
+        <v>92.051696724063802</v>
       </c>
       <c r="C215" t="s">
         <v>7</v>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="B216" s="14">
         <f t="shared" si="4"/>
-        <v>1.1401403860350441E-4</v>
+        <v>1.1401403860350441E-6</v>
       </c>
       <c r="C216" t="s">
         <v>6</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="B217" s="14">
         <f t="shared" si="4"/>
-        <v>4.974092972672592E-5</v>
+        <v>4.9740929726725927E-7</v>
       </c>
       <c r="C217" t="s">
         <v>6</v>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="B218" s="14">
         <f t="shared" si="4"/>
-        <v>-20749833.479528625</v>
+        <v>-207498.33479528627</v>
       </c>
       <c r="C218" t="s">
         <v>7</v>
@@ -5332,7 +5332,7 @@
       </c>
       <c r="B219" s="14">
         <f t="shared" si="4"/>
-        <v>3.1248620415529949E-4</v>
+        <v>3.1248620415529958E-6</v>
       </c>
       <c r="C219" t="s">
         <v>7</v>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="B220" s="14">
         <f t="shared" si="4"/>
-        <v>248.72314590785399</v>
+        <v>2.48723145907854</v>
       </c>
       <c r="C220" t="s">
         <v>7</v>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="B221" s="14">
         <f t="shared" si="4"/>
-        <v>8740.9250487155969</v>
+        <v>87.409250487155973</v>
       </c>
       <c r="C221" t="s">
         <v>7</v>
@@ -5404,7 +5404,7 @@
       </c>
       <c r="B222" s="14">
         <f t="shared" si="4"/>
-        <v>-11848542.673059383</v>
+        <v>-118485.42673059386</v>
       </c>
       <c r="C222" t="s">
         <v>7</v>
@@ -5427,8 +5427,8 @@
         <v>76</v>
       </c>
       <c r="B223" s="14">
-        <f>H223*0.09/0.8121/$H$224</f>
-        <v>6.8144907513998418E-2</v>
+        <f t="shared" si="4"/>
+        <v>6.8144907513998428E-4</v>
       </c>
       <c r="C223" t="s">
         <v>7</v>
@@ -5475,8 +5475,8 @@
         <v>115</v>
       </c>
       <c r="B225" s="14">
-        <f>H225*0.09/0.8121/$H$224</f>
-        <v>0.18489016151185533</v>
+        <f>H225*0.09/81.21/$H$224</f>
+        <v>1.8489016151185533E-3</v>
       </c>
       <c r="C225" t="s">
         <v>7</v>
@@ -5496,8 +5496,8 @@
         <v>116</v>
       </c>
       <c r="B226" s="14">
-        <f t="shared" ref="B226:B285" si="5">H226*0.09/0.8121/$H$224</f>
-        <v>1.1035837361704857E-3</v>
+        <f t="shared" ref="B226:B269" si="5">H226*0.09/81.21/$H$224</f>
+        <v>1.1035837361704857E-5</v>
       </c>
       <c r="C226" t="s">
         <v>7</v>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="B227" s="14">
         <f t="shared" si="5"/>
-        <v>8.276878021278633E-3</v>
+        <v>8.2768780212786336E-5</v>
       </c>
       <c r="C227" t="s">
         <v>7</v>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="B228" s="14">
         <f t="shared" si="5"/>
-        <v>6.3360284703460968E-3</v>
+        <v>6.3360284703460964E-5</v>
       </c>
       <c r="C228" t="s">
         <v>7</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="B229" s="14">
         <f t="shared" si="5"/>
-        <v>2.2881396560808968E-6</v>
+        <v>2.2881396560808969E-8</v>
       </c>
       <c r="C229" t="s">
         <v>7</v>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="B230" s="14">
         <f t="shared" si="5"/>
-        <v>1.4354715473383784E-2</v>
+        <v>1.4354715473383786E-4</v>
       </c>
       <c r="C230" t="s">
         <v>7</v>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="B231" s="14">
         <f t="shared" si="5"/>
-        <v>22.374153059279706</v>
+        <v>0.22374153059279706</v>
       </c>
       <c r="C231" t="s">
         <v>7</v>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="B232" s="14">
         <f t="shared" si="5"/>
-        <v>5.5179186808524114E-2</v>
+        <v>5.5179186808524121E-4</v>
       </c>
       <c r="C232" t="s">
         <v>7</v>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="B233" s="14">
         <f t="shared" si="5"/>
-        <v>6.0697105489376552E-4</v>
+        <v>6.0697105489376555E-6</v>
       </c>
       <c r="C233" t="s">
         <v>7</v>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="B234" s="14">
         <f t="shared" si="5"/>
-        <v>6.7805072820432217E-4</v>
+        <v>6.7805072820432212E-6</v>
       </c>
       <c r="C234" t="s">
         <v>7</v>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="B235" s="14">
         <f t="shared" si="5"/>
-        <v>1473.0191424763393</v>
+        <v>14.730191424763396</v>
       </c>
       <c r="C235" t="s">
         <v>7</v>
@@ -5707,7 +5707,7 @@
       </c>
       <c r="B236" s="14">
         <f t="shared" si="5"/>
-        <v>6847.4249886422931</v>
+        <v>68.474249886422925</v>
       </c>
       <c r="C236" t="s">
         <v>7</v>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="B237" s="14">
         <f t="shared" si="5"/>
-        <v>1199.5475393157442</v>
+        <v>11.995475393157443</v>
       </c>
       <c r="C237" t="s">
         <v>7</v>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="B238" s="14">
         <f t="shared" si="5"/>
-        <v>0.55179186808524094</v>
+        <v>5.5179186808524102E-3</v>
       </c>
       <c r="C238" t="s">
         <v>7</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="B239" s="14">
         <f t="shared" si="5"/>
-        <v>1.1738297265090631E-3</v>
+        <v>1.1738297265090634E-5</v>
       </c>
       <c r="C239" t="s">
         <v>7</v>
@@ -5791,7 +5791,7 @@
       </c>
       <c r="B240" s="14">
         <f t="shared" si="5"/>
-        <v>0.11035837361704856</v>
+        <v>1.1035837361704859E-3</v>
       </c>
       <c r="C240" t="s">
         <v>7</v>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="B241" s="14">
         <f t="shared" si="5"/>
-        <v>1.6772033996133781E-3</v>
+        <v>1.6772033996133784E-5</v>
       </c>
       <c r="C241" t="s">
         <v>7</v>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="B242" s="14">
         <f t="shared" si="5"/>
-        <v>22.373887989738972</v>
+        <v>0.22373887989738975</v>
       </c>
       <c r="C242" t="s">
         <v>7</v>
@@ -5854,7 +5854,7 @@
       </c>
       <c r="B243" s="14">
         <f t="shared" si="5"/>
-        <v>40784.616331025267</v>
+        <v>407.84616331025268</v>
       </c>
       <c r="C243" t="s">
         <v>7</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="B244" s="14">
         <f t="shared" si="5"/>
-        <v>0.27589593404262047</v>
+        <v>2.7589593404262051E-3</v>
       </c>
       <c r="C244" t="s">
         <v>7</v>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="B245" s="14">
         <f t="shared" si="5"/>
-        <v>1.6998721031437136E-2</v>
+        <v>1.6998721031437136E-4</v>
       </c>
       <c r="C245" t="s">
         <v>7</v>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="B246" s="14">
         <f t="shared" si="5"/>
-        <v>6.9458400948994221E-11</v>
+        <v>6.9458400948994221E-13</v>
       </c>
       <c r="C246" t="s">
         <v>7</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="B247" s="14">
         <f t="shared" si="5"/>
-        <v>7.3343787633849784</v>
+        <v>7.33437876338498E-2</v>
       </c>
       <c r="C247" t="s">
         <v>7</v>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="B248" s="14">
         <f t="shared" si="5"/>
-        <v>11.095787130595255</v>
+        <v>0.11095787130595255</v>
       </c>
       <c r="C248" t="s">
         <v>7</v>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="B249" s="14">
         <f t="shared" si="5"/>
-        <v>8.7528647841714768</v>
+        <v>8.7528647841714796E-2</v>
       </c>
       <c r="C249" t="s">
         <v>7</v>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="B250" s="14">
         <f t="shared" si="5"/>
-        <v>5.2420227468097886</v>
+        <v>5.242022746809788E-2</v>
       </c>
       <c r="C250" t="s">
         <v>7</v>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="B251" s="14">
         <f t="shared" si="5"/>
-        <v>22893668.691202644</v>
+        <v>228936.68691202646</v>
       </c>
       <c r="C251" t="s">
         <v>7</v>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="B252" s="14">
         <f t="shared" si="5"/>
-        <v>0.38700743349193673</v>
+        <v>3.8700743349193677E-3</v>
       </c>
       <c r="C252" t="s">
         <v>7</v>
@@ -6064,7 +6064,7 @@
       </c>
       <c r="B253" s="14">
         <f t="shared" si="5"/>
-        <v>0.62403689443764121</v>
+        <v>6.2403689443764126E-3</v>
       </c>
       <c r="C253" t="s">
         <v>7</v>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="B254" s="14">
         <f t="shared" si="5"/>
-        <v>7.7250861531933876E-2</v>
+        <v>7.7250861531933887E-4</v>
       </c>
       <c r="C254" t="s">
         <v>7</v>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="B255" s="14">
         <f t="shared" si="5"/>
-        <v>6.0082845314484287E-3</v>
+        <v>6.0082845314484289E-5</v>
       </c>
       <c r="C255" t="s">
         <v>7</v>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="B256" s="14">
         <f t="shared" si="5"/>
-        <v>5.2420227468097886</v>
+        <v>5.242022746809788E-2</v>
       </c>
       <c r="C256" t="s">
         <v>7</v>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="B257" s="14">
         <f t="shared" si="5"/>
-        <v>5.2953267925213647E-2</v>
+        <v>5.2953267925213651E-4</v>
       </c>
       <c r="C257" t="s">
         <v>7</v>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="B258" s="14">
         <f t="shared" si="5"/>
-        <v>2.7589593404262055E-4</v>
+        <v>2.7589593404262055E-6</v>
       </c>
       <c r="C258" t="s">
         <v>7</v>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="B259" s="14">
         <f t="shared" si="5"/>
-        <v>8.0825131351627681E-5</v>
+        <v>8.0825131351627701E-7</v>
       </c>
       <c r="C259" t="s">
         <v>7</v>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="B260" s="14">
         <f t="shared" si="5"/>
-        <v>2861.4798592812795</v>
+        <v>28.6147985928128</v>
       </c>
       <c r="C260" t="s">
         <v>7</v>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="B261" s="14">
         <f t="shared" si="5"/>
-        <v>1.7582362926694162E-9</v>
+        <v>1.7582362926694162E-11</v>
       </c>
       <c r="C261" t="s">
         <v>7</v>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="B262" s="14">
         <f t="shared" si="5"/>
-        <v>0.44143349446819208</v>
+        <v>4.4143349446819219E-3</v>
       </c>
       <c r="C262" t="s">
         <v>7</v>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="B263" s="14">
         <f t="shared" si="5"/>
-        <v>5.2227258896705125E-2</v>
+        <v>5.2227258896705129E-4</v>
       </c>
       <c r="C263" t="s">
         <v>7</v>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="B264" s="14">
         <f t="shared" si="5"/>
-        <v>6.5800223448262687E-3</v>
+        <v>6.5800223448262687E-5</v>
       </c>
       <c r="C264" t="s">
         <v>7</v>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="B265" s="14">
         <f t="shared" si="5"/>
-        <v>48.832857186863002</v>
+        <v>0.4883285718686301</v>
       </c>
       <c r="C265" t="s">
         <v>7</v>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="B266" s="14">
         <f t="shared" si="5"/>
-        <v>631.39375863893247</v>
+        <v>6.3139375863893257</v>
       </c>
       <c r="C266" t="s">
         <v>64</v>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="B267" s="14">
         <f t="shared" si="5"/>
-        <v>271.23076488657267</v>
+        <v>2.712307648865727</v>
       </c>
       <c r="C267" t="s">
         <v>7</v>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="B268" s="14">
         <f t="shared" si="5"/>
-        <v>2805.8151608249559</v>
+        <v>28.058151608249563</v>
       </c>
       <c r="C268" t="s">
         <v>7</v>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="B269" s="14">
         <f t="shared" si="5"/>
-        <v>2440.8727551408833</v>
+        <v>24.408727551408834</v>
       </c>
       <c r="C269" t="s">
         <v>7</v>
@@ -6441,8 +6441,8 @@
         <v>36</v>
       </c>
       <c r="B271" s="14">
-        <f t="shared" si="5"/>
-        <v>113.91021994428307</v>
+        <f>H271*0.09/81.21/$H$224</f>
+        <v>1.1391021994428308</v>
       </c>
       <c r="C271" t="s">
         <v>7</v>
@@ -6462,8 +6462,8 @@
         <v>137</v>
       </c>
       <c r="B272" s="14">
-        <f t="shared" si="5"/>
-        <v>2.7589593404262055E-4</v>
+        <f t="shared" ref="B272:B285" si="6">H272*0.09/81.21/$H$224</f>
+        <v>2.7589593404262055E-6</v>
       </c>
       <c r="C272" t="s">
         <v>7</v>
@@ -6483,8 +6483,8 @@
         <v>138</v>
       </c>
       <c r="B273" s="14">
-        <f t="shared" si="5"/>
-        <v>13.777464632312952</v>
+        <f t="shared" si="6"/>
+        <v>0.13777464632312955</v>
       </c>
       <c r="C273" t="s">
         <v>7</v>
@@ -6504,8 +6504,8 @@
         <v>30</v>
       </c>
       <c r="B274" s="14">
-        <f t="shared" si="5"/>
-        <v>5060.53860087254</v>
+        <f t="shared" si="6"/>
+        <v>50.605386008725411</v>
       </c>
       <c r="C274" t="s">
         <v>7</v>
@@ -6525,8 +6525,8 @@
         <v>139</v>
       </c>
       <c r="B275" s="14">
-        <f t="shared" si="5"/>
-        <v>9.8095871700095127</v>
+        <f t="shared" si="6"/>
+        <v>9.8095871700095122E-2</v>
       </c>
       <c r="C275" t="s">
         <v>7</v>
@@ -6546,8 +6546,8 @@
         <v>38</v>
       </c>
       <c r="B276" s="14">
-        <f t="shared" si="5"/>
-        <v>8.7525752122162004</v>
+        <f t="shared" si="6"/>
+        <v>8.7525752122162029E-2</v>
       </c>
       <c r="C276" t="s">
         <v>7</v>
@@ -6567,8 +6567,8 @@
         <v>62</v>
       </c>
       <c r="B277" s="14">
-        <f t="shared" si="5"/>
-        <v>20.992081938025514</v>
+        <f t="shared" si="6"/>
+        <v>0.20992081938025517</v>
       </c>
       <c r="C277" t="s">
         <v>65</v>
@@ -6588,8 +6588,8 @@
         <v>63</v>
       </c>
       <c r="B278" s="14">
-        <f t="shared" si="5"/>
-        <v>20.992081938025514</v>
+        <f t="shared" si="6"/>
+        <v>0.20992081938025517</v>
       </c>
       <c r="C278" t="s">
         <v>65</v>
@@ -6609,8 +6609,8 @@
         <v>21</v>
       </c>
       <c r="B279" s="14">
-        <f t="shared" si="5"/>
-        <v>1074.0524989970691</v>
+        <f t="shared" si="6"/>
+        <v>10.740524989970691</v>
       </c>
       <c r="C279" t="s">
         <v>22</v>
@@ -6630,8 +6630,8 @@
         <v>21</v>
       </c>
       <c r="B280" s="14">
-        <f t="shared" si="5"/>
-        <v>6.7891150343616327E-2</v>
+        <f t="shared" si="6"/>
+        <v>6.7891150343616334E-4</v>
       </c>
       <c r="C280" t="s">
         <v>22</v>
@@ -6651,8 +6651,8 @@
         <v>21</v>
       </c>
       <c r="B281" s="14">
-        <f t="shared" si="5"/>
-        <v>1074.0405182058325</v>
+        <f t="shared" si="6"/>
+        <v>10.740405182058328</v>
       </c>
       <c r="C281" t="s">
         <v>22</v>
@@ -6672,8 +6672,8 @@
         <v>33</v>
       </c>
       <c r="B282" s="14">
-        <f t="shared" si="5"/>
-        <v>11942.367029305999</v>
+        <f t="shared" si="6"/>
+        <v>119.42367029306</v>
       </c>
       <c r="C282" t="s">
         <v>22</v>
@@ -6693,8 +6693,8 @@
         <v>32</v>
       </c>
       <c r="B283" s="14">
-        <f t="shared" si="5"/>
-        <v>0.1211654292197253</v>
+        <f t="shared" si="6"/>
+        <v>1.2116542921972533E-3</v>
       </c>
       <c r="C283" t="s">
         <v>22</v>
@@ -6714,8 +6714,8 @@
         <v>140</v>
       </c>
       <c r="B284" s="14">
-        <f t="shared" si="5"/>
-        <v>1.0484045493619594</v>
+        <f t="shared" si="6"/>
+        <v>1.0484045493619596E-2</v>
       </c>
       <c r="C284" t="s">
         <v>7</v>
@@ -6735,8 +6735,8 @@
         <v>140</v>
       </c>
       <c r="B285" s="14">
-        <f t="shared" si="5"/>
-        <v>0.16288344861257056</v>
+        <f t="shared" si="6"/>
+        <v>1.6288344861257059E-3</v>
       </c>
       <c r="C285" t="s">
         <v>7</v>
